--- a/komazawa/2026/ict/ict7.xlsx
+++ b/komazawa/2026/ict/ict7.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\reput\Desktop\projects\sites\lecture-files\komazawa\2026\ict\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F0E40A81-C13C-4A29-9E76-9C376342445E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7E08DAEE-2C1B-4773-AAD9-ABB5E8EF3A28}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="5400" yWindow="5400" windowWidth="34560" windowHeight="18540" xr2:uid="{C4653102-147E-42F8-92BD-3ECA9A2E162A}"/>
+    <workbookView xWindow="5748" yWindow="5748" windowWidth="34560" windowHeight="18540" xr2:uid="{C4653102-147E-42F8-92BD-3ECA9A2E162A}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -559,12 +559,6 @@
     <t>ニューヨーク</t>
   </si>
   <si>
-    <t>上記のデータをもとに積み上げ棒グラフを作成してください。グラフはこの下に配置してください。</t>
-  </si>
-  <si>
-    <t>上記のデータをもとに折れ線グラフを作成してください。グラフはこの下に配置してください。</t>
-  </si>
-  <si>
     <t>世界の各都市の気温</t>
   </si>
   <si>
@@ -738,6 +732,12 @@
   </si>
   <si>
     <t>2025 年</t>
+  </si>
+  <si>
+    <t>上記のデータをもとに読みやすい折れ線グラフを作成してください。グラフはこの下に配置してください。</t>
+  </si>
+  <si>
+    <t>上記のデータをもとに読みやすい積み上げ棒グラフを作成してください。グラフはこの下に配置してください。</t>
   </si>
 </sst>
 </file>
@@ -989,7 +989,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="46">
+  <cellXfs count="45">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1040,6 +1040,15 @@
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
@@ -1115,18 +1124,6 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -1588,52 +1585,52 @@
       <c r="I14" s="4"/>
     </row>
     <row r="17" spans="2:9">
-      <c r="B17" s="17" t="s">
+      <c r="B17" s="20" t="s">
         <v>29</v>
       </c>
-      <c r="C17" s="18"/>
-      <c r="D17" s="18"/>
-      <c r="E17" s="18"/>
-      <c r="F17" s="18"/>
-      <c r="G17" s="18"/>
-      <c r="H17" s="18"/>
-      <c r="I17" s="18"/>
+      <c r="C17" s="21"/>
+      <c r="D17" s="21"/>
+      <c r="E17" s="21"/>
+      <c r="F17" s="21"/>
+      <c r="G17" s="21"/>
+      <c r="H17" s="21"/>
+      <c r="I17" s="21"/>
     </row>
     <row r="18" spans="2:9">
-      <c r="B18" s="18"/>
-      <c r="C18" s="18"/>
-      <c r="D18" s="18"/>
-      <c r="E18" s="18"/>
-      <c r="F18" s="18"/>
-      <c r="G18" s="18"/>
-      <c r="H18" s="18"/>
-      <c r="I18" s="18"/>
+      <c r="B18" s="21"/>
+      <c r="C18" s="21"/>
+      <c r="D18" s="21"/>
+      <c r="E18" s="21"/>
+      <c r="F18" s="21"/>
+      <c r="G18" s="21"/>
+      <c r="H18" s="21"/>
+      <c r="I18" s="21"/>
     </row>
     <row r="19" spans="2:9">
-      <c r="B19" s="18"/>
-      <c r="C19" s="18"/>
-      <c r="D19" s="18"/>
-      <c r="E19" s="18"/>
-      <c r="F19" s="18"/>
-      <c r="G19" s="18"/>
-      <c r="H19" s="18"/>
-      <c r="I19" s="18"/>
+      <c r="B19" s="21"/>
+      <c r="C19" s="21"/>
+      <c r="D19" s="21"/>
+      <c r="E19" s="21"/>
+      <c r="F19" s="21"/>
+      <c r="G19" s="21"/>
+      <c r="H19" s="21"/>
+      <c r="I19" s="21"/>
     </row>
     <row r="21" spans="2:9">
-      <c r="E21" s="19" t="s">
+      <c r="E21" s="22" t="s">
         <v>30</v>
       </c>
-      <c r="F21" s="20"/>
-      <c r="G21" s="20"/>
-      <c r="H21" s="20"/>
-      <c r="I21" s="21"/>
+      <c r="F21" s="23"/>
+      <c r="G21" s="23"/>
+      <c r="H21" s="23"/>
+      <c r="I21" s="24"/>
     </row>
     <row r="22" spans="2:9">
-      <c r="E22" s="22"/>
-      <c r="F22" s="23"/>
-      <c r="G22" s="23"/>
-      <c r="H22" s="23"/>
-      <c r="I22" s="24"/>
+      <c r="E22" s="25"/>
+      <c r="F22" s="26"/>
+      <c r="G22" s="26"/>
+      <c r="H22" s="26"/>
+      <c r="I22" s="27"/>
     </row>
   </sheetData>
   <mergeCells count="2">
@@ -1757,15 +1754,15 @@
       <c r="B11" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="D11" s="25" t="s">
-        <v>128</v>
-      </c>
-      <c r="E11" s="26"/>
-      <c r="F11" s="26"/>
-      <c r="G11" s="26"/>
-      <c r="H11" s="26"/>
-      <c r="I11" s="26"/>
-      <c r="J11" s="27"/>
+      <c r="D11" s="28" t="s">
+        <v>126</v>
+      </c>
+      <c r="E11" s="29"/>
+      <c r="F11" s="29"/>
+      <c r="G11" s="29"/>
+      <c r="H11" s="29"/>
+      <c r="I11" s="29"/>
+      <c r="J11" s="30"/>
     </row>
     <row r="12" spans="1:10">
       <c r="A12" s="1">
@@ -1774,13 +1771,13 @@
       <c r="B12" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="D12" s="28"/>
-      <c r="E12" s="29"/>
-      <c r="F12" s="29"/>
-      <c r="G12" s="29"/>
-      <c r="H12" s="29"/>
-      <c r="I12" s="29"/>
-      <c r="J12" s="30"/>
+      <c r="D12" s="31"/>
+      <c r="E12" s="32"/>
+      <c r="F12" s="32"/>
+      <c r="G12" s="32"/>
+      <c r="H12" s="32"/>
+      <c r="I12" s="32"/>
+      <c r="J12" s="33"/>
     </row>
     <row r="13" spans="1:10">
       <c r="A13" s="1">
@@ -1789,13 +1786,13 @@
       <c r="B13" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="D13" s="28"/>
-      <c r="E13" s="29"/>
-      <c r="F13" s="29"/>
-      <c r="G13" s="29"/>
-      <c r="H13" s="29"/>
-      <c r="I13" s="29"/>
-      <c r="J13" s="30"/>
+      <c r="D13" s="31"/>
+      <c r="E13" s="32"/>
+      <c r="F13" s="32"/>
+      <c r="G13" s="32"/>
+      <c r="H13" s="32"/>
+      <c r="I13" s="32"/>
+      <c r="J13" s="33"/>
     </row>
     <row r="14" spans="1:10">
       <c r="A14" s="1">
@@ -1804,13 +1801,13 @@
       <c r="B14" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="D14" s="28"/>
-      <c r="E14" s="29"/>
-      <c r="F14" s="29"/>
-      <c r="G14" s="29"/>
-      <c r="H14" s="29"/>
-      <c r="I14" s="29"/>
-      <c r="J14" s="30"/>
+      <c r="D14" s="31"/>
+      <c r="E14" s="32"/>
+      <c r="F14" s="32"/>
+      <c r="G14" s="32"/>
+      <c r="H14" s="32"/>
+      <c r="I14" s="32"/>
+      <c r="J14" s="33"/>
     </row>
     <row r="15" spans="1:10">
       <c r="A15" s="1">
@@ -1819,13 +1816,13 @@
       <c r="B15" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="D15" s="31"/>
-      <c r="E15" s="32"/>
-      <c r="F15" s="32"/>
-      <c r="G15" s="32"/>
-      <c r="H15" s="32"/>
-      <c r="I15" s="32"/>
-      <c r="J15" s="33"/>
+      <c r="D15" s="34"/>
+      <c r="E15" s="35"/>
+      <c r="F15" s="35"/>
+      <c r="G15" s="35"/>
+      <c r="H15" s="35"/>
+      <c r="I15" s="35"/>
+      <c r="J15" s="36"/>
     </row>
     <row r="16" spans="1:10">
       <c r="A16" s="1">
@@ -1850,13 +1847,13 @@
       <c r="B18" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="D18" s="19" t="s">
+      <c r="D18" s="22" t="s">
         <v>30</v>
       </c>
-      <c r="E18" s="20"/>
-      <c r="F18" s="20"/>
-      <c r="G18" s="20"/>
-      <c r="H18" s="21"/>
+      <c r="E18" s="23"/>
+      <c r="F18" s="23"/>
+      <c r="G18" s="23"/>
+      <c r="H18" s="24"/>
     </row>
     <row r="19" spans="1:8">
       <c r="A19" s="1">
@@ -1865,11 +1862,11 @@
       <c r="B19" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="D19" s="22"/>
-      <c r="E19" s="23"/>
-      <c r="F19" s="23"/>
-      <c r="G19" s="23"/>
-      <c r="H19" s="24"/>
+      <c r="D19" s="25"/>
+      <c r="E19" s="26"/>
+      <c r="F19" s="26"/>
+      <c r="G19" s="26"/>
+      <c r="H19" s="27"/>
     </row>
     <row r="20" spans="1:8">
       <c r="A20" s="1">
@@ -2409,36 +2406,36 @@
     </row>
     <row r="2" spans="1:13">
       <c r="A2" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
     </row>
     <row r="4" spans="1:13">
-      <c r="C4" s="34" t="s">
-        <v>155</v>
-      </c>
-      <c r="D4" s="35"/>
-      <c r="E4" s="35"/>
-      <c r="F4" s="35"/>
-      <c r="G4" s="35"/>
-      <c r="H4" s="35"/>
-      <c r="I4" s="35"/>
-      <c r="J4" s="35"/>
-      <c r="K4" s="35"/>
-      <c r="L4" s="35"/>
-      <c r="M4" s="36"/>
+      <c r="C4" s="37" t="s">
+        <v>153</v>
+      </c>
+      <c r="D4" s="38"/>
+      <c r="E4" s="38"/>
+      <c r="F4" s="38"/>
+      <c r="G4" s="38"/>
+      <c r="H4" s="38"/>
+      <c r="I4" s="38"/>
+      <c r="J4" s="38"/>
+      <c r="K4" s="38"/>
+      <c r="L4" s="38"/>
+      <c r="M4" s="39"/>
     </row>
     <row r="5" spans="1:13" ht="15" thickBot="1">
-      <c r="C5" s="37"/>
-      <c r="D5" s="38"/>
-      <c r="E5" s="38"/>
-      <c r="F5" s="39"/>
-      <c r="G5" s="39"/>
-      <c r="H5" s="39"/>
-      <c r="I5" s="39"/>
-      <c r="J5" s="39"/>
-      <c r="K5" s="39"/>
-      <c r="L5" s="39"/>
-      <c r="M5" s="40"/>
+      <c r="C5" s="40"/>
+      <c r="D5" s="41"/>
+      <c r="E5" s="41"/>
+      <c r="F5" s="42"/>
+      <c r="G5" s="42"/>
+      <c r="H5" s="42"/>
+      <c r="I5" s="42"/>
+      <c r="J5" s="42"/>
+      <c r="K5" s="42"/>
+      <c r="L5" s="42"/>
+      <c r="M5" s="43"/>
     </row>
     <row r="6" spans="1:13" ht="15" thickBot="1">
       <c r="C6" s="11" t="s">
@@ -2452,74 +2449,74 @@
       </c>
     </row>
     <row r="8" spans="1:13">
-      <c r="C8" s="34" t="s">
-        <v>156</v>
-      </c>
-      <c r="D8" s="35"/>
-      <c r="E8" s="35"/>
-      <c r="F8" s="35"/>
-      <c r="G8" s="35"/>
-      <c r="H8" s="35"/>
-      <c r="I8" s="35"/>
-      <c r="J8" s="35"/>
-      <c r="K8" s="35"/>
-      <c r="L8" s="35"/>
-      <c r="M8" s="36"/>
+      <c r="C8" s="37" t="s">
+        <v>154</v>
+      </c>
+      <c r="D8" s="38"/>
+      <c r="E8" s="38"/>
+      <c r="F8" s="38"/>
+      <c r="G8" s="38"/>
+      <c r="H8" s="38"/>
+      <c r="I8" s="38"/>
+      <c r="J8" s="38"/>
+      <c r="K8" s="38"/>
+      <c r="L8" s="38"/>
+      <c r="M8" s="39"/>
     </row>
     <row r="9" spans="1:13" ht="15" thickBot="1">
-      <c r="C9" s="41"/>
-      <c r="D9" s="38"/>
-      <c r="E9" s="39"/>
-      <c r="F9" s="39"/>
-      <c r="G9" s="38"/>
-      <c r="H9" s="39"/>
-      <c r="I9" s="39"/>
-      <c r="J9" s="39"/>
-      <c r="K9" s="39"/>
-      <c r="L9" s="39"/>
-      <c r="M9" s="40"/>
+      <c r="C9" s="44"/>
+      <c r="D9" s="41"/>
+      <c r="E9" s="42"/>
+      <c r="F9" s="42"/>
+      <c r="G9" s="41"/>
+      <c r="H9" s="42"/>
+      <c r="I9" s="42"/>
+      <c r="J9" s="42"/>
+      <c r="K9" s="42"/>
+      <c r="L9" s="42"/>
+      <c r="M9" s="43"/>
     </row>
     <row r="10" spans="1:13" ht="15" thickBot="1">
       <c r="C10" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="D10" s="13">
         <v>0</v>
       </c>
       <c r="F10" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="G10" s="13">
         <v>0</v>
       </c>
     </row>
     <row r="12" spans="1:13">
-      <c r="C12" s="34" t="s">
-        <v>154</v>
-      </c>
-      <c r="D12" s="35"/>
-      <c r="E12" s="35"/>
-      <c r="F12" s="35"/>
-      <c r="G12" s="35"/>
-      <c r="H12" s="35"/>
-      <c r="I12" s="35"/>
-      <c r="J12" s="35"/>
-      <c r="K12" s="35"/>
-      <c r="L12" s="35"/>
-      <c r="M12" s="36"/>
+      <c r="C12" s="37" t="s">
+        <v>152</v>
+      </c>
+      <c r="D12" s="38"/>
+      <c r="E12" s="38"/>
+      <c r="F12" s="38"/>
+      <c r="G12" s="38"/>
+      <c r="H12" s="38"/>
+      <c r="I12" s="38"/>
+      <c r="J12" s="38"/>
+      <c r="K12" s="38"/>
+      <c r="L12" s="38"/>
+      <c r="M12" s="39"/>
     </row>
     <row r="13" spans="1:13" ht="15" thickBot="1">
-      <c r="C13" s="37"/>
-      <c r="D13" s="38"/>
-      <c r="E13" s="38"/>
-      <c r="F13" s="39"/>
-      <c r="G13" s="39"/>
-      <c r="H13" s="39"/>
-      <c r="I13" s="39"/>
-      <c r="J13" s="39"/>
-      <c r="K13" s="39"/>
-      <c r="L13" s="39"/>
-      <c r="M13" s="40"/>
+      <c r="C13" s="40"/>
+      <c r="D13" s="41"/>
+      <c r="E13" s="41"/>
+      <c r="F13" s="42"/>
+      <c r="G13" s="42"/>
+      <c r="H13" s="42"/>
+      <c r="I13" s="42"/>
+      <c r="J13" s="42"/>
+      <c r="K13" s="42"/>
+      <c r="L13" s="42"/>
+      <c r="M13" s="43"/>
     </row>
     <row r="14" spans="1:13" ht="15" thickBot="1">
       <c r="C14" s="11" t="s">
@@ -2555,21 +2552,21 @@
         <v>38</v>
       </c>
       <c r="H17" s="7" t="s">
+        <v>144</v>
+      </c>
+      <c r="I17" s="7" t="s">
+        <v>145</v>
+      </c>
+      <c r="J17" s="7" t="s">
         <v>146</v>
       </c>
-      <c r="I17" s="7" t="s">
-        <v>147</v>
-      </c>
-      <c r="J17" s="7" t="s">
+      <c r="K17" s="7" t="s">
         <v>148</v>
       </c>
-      <c r="K17" s="7" t="s">
-        <v>150</v>
-      </c>
       <c r="L17" s="7" t="s">
-        <v>151</v>
-      </c>
-      <c r="O17" s="42"/>
+        <v>149</v>
+      </c>
+      <c r="O17" s="17"/>
     </row>
     <row r="18" spans="1:15">
       <c r="A18" s="6">
@@ -2578,37 +2575,37 @@
       <c r="B18" s="6" t="s">
         <v>39</v>
       </c>
-      <c r="C18" s="44">
+      <c r="C18" s="1">
         <v>786</v>
       </c>
-      <c r="D18" s="44">
+      <c r="D18" s="1">
         <v>810</v>
       </c>
-      <c r="E18" s="44">
+      <c r="E18" s="1">
         <v>835</v>
       </c>
-      <c r="F18" s="44">
+      <c r="F18" s="1">
         <v>861</v>
       </c>
-      <c r="G18" s="44">
+      <c r="G18" s="1">
         <v>861</v>
       </c>
-      <c r="H18" s="44">
+      <c r="H18" s="1">
         <v>889</v>
       </c>
-      <c r="I18" s="44">
+      <c r="I18" s="1">
         <v>920</v>
       </c>
-      <c r="J18" s="44">
+      <c r="J18" s="1">
         <v>960</v>
       </c>
-      <c r="K18" s="45">
+      <c r="K18" s="19">
         <v>1010</v>
       </c>
-      <c r="L18" s="45">
+      <c r="L18" s="19">
         <v>1075</v>
       </c>
-      <c r="O18" s="43"/>
+      <c r="O18" s="18"/>
     </row>
     <row r="19" spans="1:15">
       <c r="A19" s="6">
@@ -2617,37 +2614,37 @@
       <c r="B19" s="6" t="s">
         <v>40</v>
       </c>
-      <c r="C19" s="44">
+      <c r="C19" s="1">
         <v>716</v>
       </c>
-      <c r="D19" s="44">
+      <c r="D19" s="1">
         <v>738</v>
       </c>
-      <c r="E19" s="44">
+      <c r="E19" s="1">
         <v>762</v>
       </c>
-      <c r="F19" s="44">
+      <c r="F19" s="1">
         <v>790</v>
       </c>
-      <c r="G19" s="44">
+      <c r="G19" s="1">
         <v>793</v>
       </c>
-      <c r="H19" s="44">
+      <c r="H19" s="1">
         <v>822</v>
       </c>
-      <c r="I19" s="44">
+      <c r="I19" s="1">
         <v>853</v>
       </c>
-      <c r="J19" s="44">
+      <c r="J19" s="1">
         <v>898</v>
       </c>
-      <c r="K19" s="45">
+      <c r="K19" s="19">
         <v>953</v>
       </c>
-      <c r="L19" s="45">
+      <c r="L19" s="19">
         <v>1029</v>
       </c>
-      <c r="O19" s="43"/>
+      <c r="O19" s="18"/>
     </row>
     <row r="20" spans="1:15">
       <c r="A20" s="6">
@@ -2656,37 +2653,37 @@
       <c r="B20" s="6" t="s">
         <v>41</v>
       </c>
-      <c r="C20" s="44">
+      <c r="C20" s="1">
         <v>716</v>
       </c>
-      <c r="D20" s="44">
+      <c r="D20" s="1">
         <v>738</v>
       </c>
-      <c r="E20" s="44">
+      <c r="E20" s="1">
         <v>762</v>
       </c>
-      <c r="F20" s="44">
+      <c r="F20" s="1">
         <v>790</v>
       </c>
-      <c r="G20" s="44">
+      <c r="G20" s="1">
         <v>793</v>
       </c>
-      <c r="H20" s="44">
+      <c r="H20" s="1">
         <v>821</v>
       </c>
-      <c r="I20" s="44">
+      <c r="I20" s="1">
         <v>854</v>
       </c>
-      <c r="J20" s="44">
+      <c r="J20" s="1">
         <v>893</v>
       </c>
-      <c r="K20" s="45">
+      <c r="K20" s="19">
         <v>952</v>
       </c>
-      <c r="L20" s="45">
+      <c r="L20" s="19">
         <v>1031</v>
       </c>
-      <c r="O20" s="43"/>
+      <c r="O20" s="18"/>
     </row>
     <row r="21" spans="1:15">
       <c r="A21" s="6">
@@ -2695,37 +2692,37 @@
       <c r="B21" s="6" t="s">
         <v>42</v>
       </c>
-      <c r="C21" s="44">
+      <c r="C21" s="1">
         <v>748</v>
       </c>
-      <c r="D21" s="44">
+      <c r="D21" s="1">
         <v>772</v>
       </c>
-      <c r="E21" s="44">
+      <c r="E21" s="1">
         <v>798</v>
       </c>
-      <c r="F21" s="44">
+      <c r="F21" s="1">
         <v>824</v>
       </c>
-      <c r="G21" s="44">
+      <c r="G21" s="1">
         <v>825</v>
       </c>
-      <c r="H21" s="44">
+      <c r="H21" s="1">
         <v>853</v>
       </c>
-      <c r="I21" s="44">
+      <c r="I21" s="1">
         <v>883</v>
       </c>
-      <c r="J21" s="44">
+      <c r="J21" s="1">
         <v>923</v>
       </c>
-      <c r="K21" s="45">
+      <c r="K21" s="19">
         <v>973</v>
       </c>
-      <c r="L21" s="45">
+      <c r="L21" s="19">
         <v>1038</v>
       </c>
-      <c r="O21" s="43"/>
+      <c r="O21" s="18"/>
     </row>
     <row r="22" spans="1:15">
       <c r="A22" s="6">
@@ -2734,37 +2731,37 @@
       <c r="B22" s="6" t="s">
         <v>43</v>
       </c>
-      <c r="C22" s="44">
+      <c r="C22" s="1">
         <v>716</v>
       </c>
-      <c r="D22" s="44">
+      <c r="D22" s="1">
         <v>738</v>
       </c>
-      <c r="E22" s="44">
+      <c r="E22" s="1">
         <v>762</v>
       </c>
-      <c r="F22" s="44">
+      <c r="F22" s="1">
         <v>790</v>
       </c>
-      <c r="G22" s="44">
+      <c r="G22" s="1">
         <v>792</v>
       </c>
-      <c r="H22" s="44">
+      <c r="H22" s="1">
         <v>822</v>
       </c>
-      <c r="I22" s="44">
+      <c r="I22" s="1">
         <v>853</v>
       </c>
-      <c r="J22" s="44">
+      <c r="J22" s="1">
         <v>897</v>
       </c>
-      <c r="K22" s="45">
+      <c r="K22" s="19">
         <v>951</v>
       </c>
-      <c r="L22" s="45">
+      <c r="L22" s="19">
         <v>1031</v>
       </c>
-      <c r="O22" s="43"/>
+      <c r="O22" s="18"/>
     </row>
     <row r="23" spans="1:15">
       <c r="A23" s="6">
@@ -2773,37 +2770,37 @@
       <c r="B23" s="6" t="s">
         <v>44</v>
       </c>
-      <c r="C23" s="44">
+      <c r="C23" s="1">
         <v>717</v>
       </c>
-      <c r="D23" s="44">
+      <c r="D23" s="1">
         <v>739</v>
       </c>
-      <c r="E23" s="44">
+      <c r="E23" s="1">
         <v>763</v>
       </c>
-      <c r="F23" s="44">
+      <c r="F23" s="1">
         <v>790</v>
       </c>
-      <c r="G23" s="44">
+      <c r="G23" s="1">
         <v>793</v>
       </c>
-      <c r="H23" s="44">
+      <c r="H23" s="1">
         <v>822</v>
       </c>
-      <c r="I23" s="44">
+      <c r="I23" s="1">
         <v>854</v>
       </c>
-      <c r="J23" s="44">
+      <c r="J23" s="1">
         <v>900</v>
       </c>
-      <c r="K23" s="45">
+      <c r="K23" s="19">
         <v>955</v>
       </c>
-      <c r="L23" s="45">
+      <c r="L23" s="19">
         <v>1032</v>
       </c>
-      <c r="O23" s="43"/>
+      <c r="O23" s="18"/>
     </row>
     <row r="24" spans="1:15">
       <c r="A24" s="6">
@@ -2812,37 +2809,37 @@
       <c r="B24" s="6" t="s">
         <v>45</v>
       </c>
-      <c r="C24" s="44">
+      <c r="C24" s="1">
         <v>726</v>
       </c>
-      <c r="D24" s="44">
+      <c r="D24" s="1">
         <v>748</v>
       </c>
-      <c r="E24" s="44">
+      <c r="E24" s="1">
         <v>772</v>
       </c>
-      <c r="F24" s="44">
+      <c r="F24" s="1">
         <v>798</v>
       </c>
-      <c r="G24" s="44">
+      <c r="G24" s="1">
         <v>800</v>
       </c>
-      <c r="H24" s="44">
+      <c r="H24" s="1">
         <v>828</v>
       </c>
-      <c r="I24" s="44">
+      <c r="I24" s="1">
         <v>858</v>
       </c>
-      <c r="J24" s="44">
+      <c r="J24" s="1">
         <v>900</v>
       </c>
-      <c r="K24" s="45">
+      <c r="K24" s="19">
         <v>955</v>
       </c>
-      <c r="L24" s="45">
+      <c r="L24" s="19">
         <v>1033</v>
       </c>
-      <c r="O24" s="43"/>
+      <c r="O24" s="18"/>
     </row>
     <row r="25" spans="1:15">
       <c r="A25" s="6">
@@ -2851,37 +2848,37 @@
       <c r="B25" s="6" t="s">
         <v>46</v>
       </c>
-      <c r="C25" s="44">
+      <c r="C25" s="1">
         <v>771</v>
       </c>
-      <c r="D25" s="44">
+      <c r="D25" s="1">
         <v>796</v>
       </c>
-      <c r="E25" s="44">
+      <c r="E25" s="1">
         <v>822</v>
       </c>
-      <c r="F25" s="44">
+      <c r="F25" s="1">
         <v>849</v>
       </c>
-      <c r="G25" s="44">
+      <c r="G25" s="1">
         <v>851</v>
       </c>
-      <c r="H25" s="44">
+      <c r="H25" s="1">
         <v>879</v>
       </c>
-      <c r="I25" s="44">
+      <c r="I25" s="1">
         <v>911</v>
       </c>
-      <c r="J25" s="44">
+      <c r="J25" s="1">
         <v>953</v>
       </c>
-      <c r="K25" s="45">
+      <c r="K25" s="19">
         <v>1005</v>
       </c>
-      <c r="L25" s="45">
+      <c r="L25" s="19">
         <v>1074</v>
       </c>
-      <c r="O25" s="43"/>
+      <c r="O25" s="18"/>
     </row>
     <row r="26" spans="1:15">
       <c r="A26" s="6">
@@ -2890,37 +2887,37 @@
       <c r="B26" s="6" t="s">
         <v>47</v>
       </c>
-      <c r="C26" s="44">
+      <c r="C26" s="1">
         <v>775</v>
       </c>
-      <c r="D26" s="44">
+      <c r="D26" s="1">
         <v>800</v>
       </c>
-      <c r="E26" s="44">
+      <c r="E26" s="1">
         <v>826</v>
       </c>
-      <c r="F26" s="44">
+      <c r="F26" s="1">
         <v>853</v>
       </c>
-      <c r="G26" s="44">
+      <c r="G26" s="1">
         <v>854</v>
       </c>
-      <c r="H26" s="44">
+      <c r="H26" s="1">
         <v>882</v>
       </c>
-      <c r="I26" s="44">
+      <c r="I26" s="1">
         <v>913</v>
       </c>
-      <c r="J26" s="44">
+      <c r="J26" s="1">
         <v>954</v>
       </c>
-      <c r="K26" s="45">
+      <c r="K26" s="19">
         <v>1004</v>
       </c>
-      <c r="L26" s="45">
+      <c r="L26" s="19">
         <v>1068</v>
       </c>
-      <c r="O26" s="43"/>
+      <c r="O26" s="18"/>
     </row>
     <row r="27" spans="1:15">
       <c r="A27" s="6">
@@ -2929,37 +2926,37 @@
       <c r="B27" s="6" t="s">
         <v>48</v>
       </c>
-      <c r="C27" s="44">
+      <c r="C27" s="1">
         <v>759</v>
       </c>
-      <c r="D27" s="44">
+      <c r="D27" s="1">
         <v>783</v>
       </c>
-      <c r="E27" s="44">
+      <c r="E27" s="1">
         <v>809</v>
       </c>
-      <c r="F27" s="44">
+      <c r="F27" s="1">
         <v>835</v>
       </c>
-      <c r="G27" s="44">
+      <c r="G27" s="1">
         <v>837</v>
       </c>
-      <c r="H27" s="44">
+      <c r="H27" s="1">
         <v>865</v>
       </c>
-      <c r="I27" s="44">
+      <c r="I27" s="1">
         <v>895</v>
       </c>
-      <c r="J27" s="44">
+      <c r="J27" s="1">
         <v>935</v>
       </c>
-      <c r="K27" s="45">
+      <c r="K27" s="19">
         <v>985</v>
       </c>
-      <c r="L27" s="45">
+      <c r="L27" s="19">
         <v>1063</v>
       </c>
-      <c r="O27" s="43"/>
+      <c r="O27" s="18"/>
     </row>
     <row r="28" spans="1:15">
       <c r="A28" s="6">
@@ -2968,37 +2965,37 @@
       <c r="B28" s="6" t="s">
         <v>49</v>
       </c>
-      <c r="C28" s="44">
+      <c r="C28" s="1">
         <v>845</v>
       </c>
-      <c r="D28" s="44">
+      <c r="D28" s="1">
         <v>871</v>
       </c>
-      <c r="E28" s="44">
+      <c r="E28" s="1">
         <v>898</v>
       </c>
-      <c r="F28" s="44">
+      <c r="F28" s="1">
         <v>926</v>
       </c>
-      <c r="G28" s="44">
+      <c r="G28" s="1">
         <v>928</v>
       </c>
-      <c r="H28" s="44">
+      <c r="H28" s="1">
         <v>956</v>
       </c>
-      <c r="I28" s="44">
+      <c r="I28" s="1">
         <v>987</v>
       </c>
-      <c r="J28" s="44">
+      <c r="J28" s="1">
         <v>1028</v>
       </c>
-      <c r="K28" s="45">
+      <c r="K28" s="19">
         <v>1078</v>
       </c>
-      <c r="L28" s="45">
+      <c r="L28" s="19">
         <v>1141</v>
       </c>
-      <c r="O28" s="43"/>
+      <c r="O28" s="18"/>
     </row>
     <row r="29" spans="1:15">
       <c r="A29" s="6">
@@ -3007,37 +3004,37 @@
       <c r="B29" s="6" t="s">
         <v>50</v>
       </c>
-      <c r="C29" s="44">
+      <c r="C29" s="1">
         <v>842</v>
       </c>
-      <c r="D29" s="44">
+      <c r="D29" s="1">
         <v>868</v>
       </c>
-      <c r="E29" s="44">
+      <c r="E29" s="1">
         <v>895</v>
       </c>
-      <c r="F29" s="44">
+      <c r="F29" s="1">
         <v>923</v>
       </c>
-      <c r="G29" s="44">
+      <c r="G29" s="1">
         <v>925</v>
       </c>
-      <c r="H29" s="44">
+      <c r="H29" s="1">
         <v>953</v>
       </c>
-      <c r="I29" s="44">
+      <c r="I29" s="1">
         <v>984</v>
       </c>
-      <c r="J29" s="44">
+      <c r="J29" s="1">
         <v>1026</v>
       </c>
-      <c r="K29" s="45">
+      <c r="K29" s="19">
         <v>1076</v>
       </c>
-      <c r="L29" s="45">
+      <c r="L29" s="19">
         <v>1140</v>
       </c>
-      <c r="O29" s="43"/>
+      <c r="O29" s="18"/>
     </row>
     <row r="30" spans="1:15">
       <c r="A30" s="6">
@@ -3046,37 +3043,37 @@
       <c r="B30" s="6" t="s">
         <v>51</v>
       </c>
-      <c r="C30" s="44">
+      <c r="C30" s="1">
         <v>932</v>
       </c>
-      <c r="D30" s="44">
+      <c r="D30" s="1">
         <v>958</v>
       </c>
-      <c r="E30" s="44">
+      <c r="E30" s="1">
         <v>985</v>
       </c>
-      <c r="F30" s="44">
+      <c r="F30" s="1">
         <v>1013</v>
       </c>
-      <c r="G30" s="44">
+      <c r="G30" s="1">
         <v>1013</v>
       </c>
-      <c r="H30" s="44">
+      <c r="H30" s="1">
         <v>1041</v>
       </c>
-      <c r="I30" s="44">
+      <c r="I30" s="1">
         <v>1072</v>
       </c>
-      <c r="J30" s="44">
+      <c r="J30" s="1">
         <v>1113</v>
       </c>
-      <c r="K30" s="45">
+      <c r="K30" s="19">
         <v>1163</v>
       </c>
-      <c r="L30" s="45">
+      <c r="L30" s="19">
         <v>1226</v>
       </c>
-      <c r="O30" s="43"/>
+      <c r="O30" s="18"/>
     </row>
     <row r="31" spans="1:15">
       <c r="A31" s="6">
@@ -3085,37 +3082,37 @@
       <c r="B31" s="6" t="s">
         <v>52</v>
       </c>
-      <c r="C31" s="44">
+      <c r="C31" s="1">
         <v>930</v>
       </c>
-      <c r="D31" s="44">
+      <c r="D31" s="1">
         <v>956</v>
       </c>
-      <c r="E31" s="44">
+      <c r="E31" s="1">
         <v>983</v>
       </c>
-      <c r="F31" s="44">
+      <c r="F31" s="1">
         <v>1011</v>
       </c>
-      <c r="G31" s="44">
+      <c r="G31" s="1">
         <v>1012</v>
       </c>
-      <c r="H31" s="44">
+      <c r="H31" s="1">
         <v>1040</v>
       </c>
-      <c r="I31" s="44">
+      <c r="I31" s="1">
         <v>1071</v>
       </c>
-      <c r="J31" s="44">
+      <c r="J31" s="1">
         <v>1112</v>
       </c>
-      <c r="K31" s="45">
+      <c r="K31" s="19">
         <v>1162</v>
       </c>
-      <c r="L31" s="45">
+      <c r="L31" s="19">
         <v>1225</v>
       </c>
-      <c r="O31" s="43"/>
+      <c r="O31" s="18"/>
     </row>
     <row r="32" spans="1:15">
       <c r="A32" s="6">
@@ -3124,37 +3121,37 @@
       <c r="B32" s="6" t="s">
         <v>53</v>
       </c>
-      <c r="C32" s="44">
+      <c r="C32" s="1">
         <v>753</v>
       </c>
-      <c r="D32" s="44">
+      <c r="D32" s="1">
         <v>778</v>
       </c>
-      <c r="E32" s="44">
+      <c r="E32" s="1">
         <v>803</v>
       </c>
-      <c r="F32" s="44">
+      <c r="F32" s="1">
         <v>830</v>
       </c>
-      <c r="G32" s="44">
+      <c r="G32" s="1">
         <v>831</v>
       </c>
-      <c r="H32" s="44">
+      <c r="H32" s="1">
         <v>859</v>
       </c>
-      <c r="I32" s="44">
+      <c r="I32" s="1">
         <v>890</v>
       </c>
-      <c r="J32" s="44">
+      <c r="J32" s="1">
         <v>931</v>
       </c>
-      <c r="K32" s="45">
+      <c r="K32" s="19">
         <v>985</v>
       </c>
-      <c r="L32" s="45">
+      <c r="L32" s="19">
         <v>1050</v>
       </c>
-      <c r="O32" s="43"/>
+      <c r="O32" s="18"/>
     </row>
     <row r="33" spans="1:15">
       <c r="A33" s="6">
@@ -3163,37 +3160,37 @@
       <c r="B33" s="6" t="s">
         <v>54</v>
       </c>
-      <c r="C33" s="44">
+      <c r="C33" s="1">
         <v>770</v>
       </c>
-      <c r="D33" s="44">
+      <c r="D33" s="1">
         <v>795</v>
       </c>
-      <c r="E33" s="44">
+      <c r="E33" s="1">
         <v>821</v>
       </c>
-      <c r="F33" s="44">
+      <c r="F33" s="1">
         <v>848</v>
       </c>
-      <c r="G33" s="44">
+      <c r="G33" s="1">
         <v>849</v>
       </c>
-      <c r="H33" s="44">
+      <c r="H33" s="1">
         <v>877</v>
       </c>
-      <c r="I33" s="44">
+      <c r="I33" s="1">
         <v>908</v>
       </c>
-      <c r="J33" s="44">
+      <c r="J33" s="1">
         <v>948</v>
       </c>
-      <c r="K33" s="45">
+      <c r="K33" s="19">
         <v>998</v>
       </c>
-      <c r="L33" s="45">
+      <c r="L33" s="19">
         <v>1062</v>
       </c>
-      <c r="O33" s="43"/>
+      <c r="O33" s="18"/>
     </row>
     <row r="34" spans="1:15">
       <c r="A34" s="6">
@@ -3202,37 +3199,37 @@
       <c r="B34" s="6" t="s">
         <v>55</v>
       </c>
-      <c r="C34" s="44">
+      <c r="C34" s="1">
         <v>757</v>
       </c>
-      <c r="D34" s="44">
+      <c r="D34" s="1">
         <v>781</v>
       </c>
-      <c r="E34" s="44">
+      <c r="E34" s="1">
         <v>806</v>
       </c>
-      <c r="F34" s="44">
+      <c r="F34" s="1">
         <v>832</v>
       </c>
-      <c r="G34" s="44">
+      <c r="G34" s="1">
         <v>833</v>
       </c>
-      <c r="H34" s="44">
+      <c r="H34" s="1">
         <v>861</v>
       </c>
-      <c r="I34" s="44">
+      <c r="I34" s="1">
         <v>891</v>
       </c>
-      <c r="J34" s="44">
+      <c r="J34" s="1">
         <v>933</v>
       </c>
-      <c r="K34" s="45">
+      <c r="K34" s="19">
         <v>984</v>
       </c>
-      <c r="L34" s="45">
+      <c r="L34" s="19">
         <v>1054</v>
       </c>
-      <c r="O34" s="43"/>
+      <c r="O34" s="18"/>
     </row>
     <row r="35" spans="1:15">
       <c r="A35" s="6">
@@ -3241,37 +3238,37 @@
       <c r="B35" s="6" t="s">
         <v>56</v>
       </c>
-      <c r="C35" s="44">
+      <c r="C35" s="1">
         <v>754</v>
       </c>
-      <c r="D35" s="44">
+      <c r="D35" s="1">
         <v>778</v>
       </c>
-      <c r="E35" s="44">
+      <c r="E35" s="1">
         <v>803</v>
       </c>
-      <c r="F35" s="44">
+      <c r="F35" s="1">
         <v>829</v>
       </c>
-      <c r="G35" s="44">
+      <c r="G35" s="1">
         <v>830</v>
       </c>
-      <c r="H35" s="44">
+      <c r="H35" s="1">
         <v>858</v>
       </c>
-      <c r="I35" s="44">
+      <c r="I35" s="1">
         <v>888</v>
       </c>
-      <c r="J35" s="44">
+      <c r="J35" s="1">
         <v>931</v>
       </c>
-      <c r="K35" s="45">
+      <c r="K35" s="19">
         <v>984</v>
       </c>
-      <c r="L35" s="45">
+      <c r="L35" s="19">
         <v>1053</v>
       </c>
-      <c r="O35" s="43"/>
+      <c r="O35" s="18"/>
     </row>
     <row r="36" spans="1:15">
       <c r="A36" s="6">
@@ -3280,37 +3277,37 @@
       <c r="B36" s="6" t="s">
         <v>57</v>
       </c>
-      <c r="C36" s="44">
+      <c r="C36" s="1">
         <v>759</v>
       </c>
-      <c r="D36" s="44">
+      <c r="D36" s="1">
         <v>784</v>
       </c>
-      <c r="E36" s="44">
+      <c r="E36" s="1">
         <v>810</v>
       </c>
-      <c r="F36" s="44">
+      <c r="F36" s="1">
         <v>837</v>
       </c>
-      <c r="G36" s="44">
+      <c r="G36" s="1">
         <v>838</v>
       </c>
-      <c r="H36" s="44">
+      <c r="H36" s="1">
         <v>866</v>
       </c>
-      <c r="I36" s="44">
+      <c r="I36" s="1">
         <v>898</v>
       </c>
-      <c r="J36" s="44">
+      <c r="J36" s="1">
         <v>938</v>
       </c>
-      <c r="K36" s="45">
+      <c r="K36" s="19">
         <v>988</v>
       </c>
-      <c r="L36" s="45">
+      <c r="L36" s="19">
         <v>1052</v>
       </c>
-      <c r="O36" s="43"/>
+      <c r="O36" s="18"/>
     </row>
     <row r="37" spans="1:15">
       <c r="A37" s="6">
@@ -3319,37 +3316,37 @@
       <c r="B37" s="6" t="s">
         <v>58</v>
       </c>
-      <c r="C37" s="44">
+      <c r="C37" s="1">
         <v>770</v>
       </c>
-      <c r="D37" s="44">
+      <c r="D37" s="1">
         <v>795</v>
       </c>
-      <c r="E37" s="44">
+      <c r="E37" s="1">
         <v>821</v>
       </c>
-      <c r="F37" s="44">
+      <c r="F37" s="1">
         <v>848</v>
       </c>
-      <c r="G37" s="44">
+      <c r="G37" s="1">
         <v>849</v>
       </c>
-      <c r="H37" s="44">
+      <c r="H37" s="1">
         <v>877</v>
       </c>
-      <c r="I37" s="44">
+      <c r="I37" s="1">
         <v>908</v>
       </c>
-      <c r="J37" s="44">
+      <c r="J37" s="1">
         <v>948</v>
       </c>
-      <c r="K37" s="45">
+      <c r="K37" s="19">
         <v>998</v>
       </c>
-      <c r="L37" s="45">
+      <c r="L37" s="19">
         <v>1061</v>
       </c>
-      <c r="O37" s="43"/>
+      <c r="O37" s="18"/>
     </row>
     <row r="38" spans="1:15">
       <c r="A38" s="6">
@@ -3358,37 +3355,37 @@
       <c r="B38" s="6" t="s">
         <v>59</v>
       </c>
-      <c r="C38" s="44">
+      <c r="C38" s="1">
         <v>776</v>
       </c>
-      <c r="D38" s="44">
+      <c r="D38" s="1">
         <v>800</v>
       </c>
-      <c r="E38" s="44">
+      <c r="E38" s="1">
         <v>825</v>
       </c>
-      <c r="F38" s="44">
+      <c r="F38" s="1">
         <v>851</v>
       </c>
-      <c r="G38" s="44">
+      <c r="G38" s="1">
         <v>852</v>
       </c>
-      <c r="H38" s="44">
+      <c r="H38" s="1">
         <v>880</v>
       </c>
-      <c r="I38" s="44">
+      <c r="I38" s="1">
         <v>910</v>
       </c>
-      <c r="J38" s="44">
+      <c r="J38" s="1">
         <v>950</v>
       </c>
-      <c r="K38" s="45">
+      <c r="K38" s="19">
         <v>1001</v>
       </c>
-      <c r="L38" s="45">
+      <c r="L38" s="19">
         <v>1065</v>
       </c>
-      <c r="O38" s="43"/>
+      <c r="O38" s="18"/>
     </row>
     <row r="39" spans="1:15">
       <c r="A39" s="6">
@@ -3397,37 +3394,37 @@
       <c r="B39" s="6" t="s">
         <v>60</v>
       </c>
-      <c r="C39" s="44">
+      <c r="C39" s="1">
         <v>807</v>
       </c>
-      <c r="D39" s="44">
+      <c r="D39" s="1">
         <v>832</v>
       </c>
-      <c r="E39" s="44">
+      <c r="E39" s="1">
         <v>858</v>
       </c>
-      <c r="F39" s="44">
+      <c r="F39" s="1">
         <v>885</v>
       </c>
-      <c r="G39" s="44">
+      <c r="G39" s="1">
         <v>885</v>
       </c>
-      <c r="H39" s="44">
+      <c r="H39" s="1">
         <v>913</v>
       </c>
-      <c r="I39" s="44">
+      <c r="I39" s="1">
         <v>944</v>
       </c>
-      <c r="J39" s="44">
+      <c r="J39" s="1">
         <v>984</v>
       </c>
-      <c r="K39" s="45">
+      <c r="K39" s="19">
         <v>1034</v>
       </c>
-      <c r="L39" s="45">
+      <c r="L39" s="19">
         <v>1097</v>
       </c>
-      <c r="O39" s="43"/>
+      <c r="O39" s="18"/>
     </row>
     <row r="40" spans="1:15">
       <c r="A40" s="6">
@@ -3436,37 +3433,37 @@
       <c r="B40" s="6" t="s">
         <v>61</v>
       </c>
-      <c r="C40" s="44">
+      <c r="C40" s="1">
         <v>845</v>
       </c>
-      <c r="D40" s="44">
+      <c r="D40" s="1">
         <v>871</v>
       </c>
-      <c r="E40" s="44">
+      <c r="E40" s="1">
         <v>898</v>
       </c>
-      <c r="F40" s="44">
+      <c r="F40" s="1">
         <v>926</v>
       </c>
-      <c r="G40" s="44">
+      <c r="G40" s="1">
         <v>927</v>
       </c>
-      <c r="H40" s="44">
+      <c r="H40" s="1">
         <v>955</v>
       </c>
-      <c r="I40" s="44">
+      <c r="I40" s="1">
         <v>986</v>
       </c>
-      <c r="J40" s="44">
+      <c r="J40" s="1">
         <v>1027</v>
       </c>
-      <c r="K40" s="45">
+      <c r="K40" s="19">
         <v>1077</v>
       </c>
-      <c r="L40" s="45">
+      <c r="L40" s="19">
         <v>1140</v>
       </c>
-      <c r="O40" s="43"/>
+      <c r="O40" s="18"/>
     </row>
     <row r="41" spans="1:15">
       <c r="A41" s="6">
@@ -3475,37 +3472,37 @@
       <c r="B41" s="6" t="s">
         <v>62</v>
       </c>
-      <c r="C41" s="44">
+      <c r="C41" s="1">
         <v>795</v>
       </c>
-      <c r="D41" s="44">
+      <c r="D41" s="1">
         <v>820</v>
       </c>
-      <c r="E41" s="44">
+      <c r="E41" s="1">
         <v>846</v>
       </c>
-      <c r="F41" s="44">
+      <c r="F41" s="1">
         <v>873</v>
       </c>
-      <c r="G41" s="44">
+      <c r="G41" s="1">
         <v>874</v>
       </c>
-      <c r="H41" s="44">
+      <c r="H41" s="1">
         <v>902</v>
       </c>
-      <c r="I41" s="44">
+      <c r="I41" s="1">
         <v>933</v>
       </c>
-      <c r="J41" s="44">
+      <c r="J41" s="1">
         <v>973</v>
       </c>
-      <c r="K41" s="45">
+      <c r="K41" s="19">
         <v>1023</v>
       </c>
-      <c r="L41" s="45">
+      <c r="L41" s="19">
         <v>1087</v>
       </c>
-      <c r="O41" s="43"/>
+      <c r="O41" s="18"/>
     </row>
     <row r="42" spans="1:15">
       <c r="A42" s="6">
@@ -3514,37 +3511,37 @@
       <c r="B42" s="6" t="s">
         <v>63</v>
       </c>
-      <c r="C42" s="44">
+      <c r="C42" s="1">
         <v>788</v>
       </c>
-      <c r="D42" s="44">
+      <c r="D42" s="1">
         <v>813</v>
       </c>
-      <c r="E42" s="44">
+      <c r="E42" s="1">
         <v>839</v>
       </c>
-      <c r="F42" s="44">
+      <c r="F42" s="1">
         <v>866</v>
       </c>
-      <c r="G42" s="44">
+      <c r="G42" s="1">
         <v>868</v>
       </c>
-      <c r="H42" s="44">
+      <c r="H42" s="1">
         <v>896</v>
       </c>
-      <c r="I42" s="44">
+      <c r="I42" s="1">
         <v>927</v>
       </c>
-      <c r="J42" s="44">
+      <c r="J42" s="1">
         <v>967</v>
       </c>
-      <c r="K42" s="45">
+      <c r="K42" s="19">
         <v>1017</v>
       </c>
-      <c r="L42" s="45">
+      <c r="L42" s="19">
         <v>1080</v>
       </c>
-      <c r="O42" s="43"/>
+      <c r="O42" s="18"/>
     </row>
     <row r="43" spans="1:15">
       <c r="A43" s="6">
@@ -3553,37 +3550,37 @@
       <c r="B43" s="6" t="s">
         <v>64</v>
       </c>
-      <c r="C43" s="44">
+      <c r="C43" s="1">
         <v>831</v>
       </c>
-      <c r="D43" s="44">
+      <c r="D43" s="1">
         <v>856</v>
       </c>
-      <c r="E43" s="44">
+      <c r="E43" s="1">
         <v>882</v>
       </c>
-      <c r="F43" s="44">
+      <c r="F43" s="1">
         <v>909</v>
       </c>
-      <c r="G43" s="44">
+      <c r="G43" s="1">
         <v>909</v>
       </c>
-      <c r="H43" s="44">
+      <c r="H43" s="1">
         <v>937</v>
       </c>
-      <c r="I43" s="44">
+      <c r="I43" s="1">
         <v>968</v>
       </c>
-      <c r="J43" s="44">
+      <c r="J43" s="1">
         <v>1008</v>
       </c>
-      <c r="K43" s="45">
+      <c r="K43" s="19">
         <v>1058</v>
       </c>
-      <c r="L43" s="45">
+      <c r="L43" s="19">
         <v>1122</v>
       </c>
-      <c r="O43" s="43"/>
+      <c r="O43" s="18"/>
     </row>
     <row r="44" spans="1:15">
       <c r="A44" s="6">
@@ -3592,37 +3589,37 @@
       <c r="B44" s="6" t="s">
         <v>65</v>
       </c>
-      <c r="C44" s="44">
+      <c r="C44" s="1">
         <v>883</v>
       </c>
-      <c r="D44" s="44">
+      <c r="D44" s="1">
         <v>909</v>
       </c>
-      <c r="E44" s="44">
+      <c r="E44" s="1">
         <v>936</v>
       </c>
-      <c r="F44" s="44">
+      <c r="F44" s="1">
         <v>964</v>
       </c>
-      <c r="G44" s="44">
+      <c r="G44" s="1">
         <v>964</v>
       </c>
-      <c r="H44" s="44">
+      <c r="H44" s="1">
         <v>992</v>
       </c>
-      <c r="I44" s="44">
+      <c r="I44" s="1">
         <v>1023</v>
       </c>
-      <c r="J44" s="44">
+      <c r="J44" s="1">
         <v>1064</v>
       </c>
-      <c r="K44" s="45">
+      <c r="K44" s="19">
         <v>1114</v>
       </c>
-      <c r="L44" s="45">
+      <c r="L44" s="19">
         <v>1177</v>
       </c>
-      <c r="O44" s="43"/>
+      <c r="O44" s="18"/>
     </row>
     <row r="45" spans="1:15">
       <c r="A45" s="6">
@@ -3631,37 +3628,37 @@
       <c r="B45" s="6" t="s">
         <v>66</v>
       </c>
-      <c r="C45" s="44">
+      <c r="C45" s="1">
         <v>819</v>
       </c>
-      <c r="D45" s="44">
+      <c r="D45" s="1">
         <v>844</v>
       </c>
-      <c r="E45" s="44">
+      <c r="E45" s="1">
         <v>871</v>
       </c>
-      <c r="F45" s="44">
+      <c r="F45" s="1">
         <v>899</v>
       </c>
-      <c r="G45" s="44">
+      <c r="G45" s="1">
         <v>900</v>
       </c>
-      <c r="H45" s="44">
+      <c r="H45" s="1">
         <v>928</v>
       </c>
-      <c r="I45" s="44">
+      <c r="I45" s="1">
         <v>960</v>
       </c>
-      <c r="J45" s="44">
+      <c r="J45" s="1">
         <v>1001</v>
       </c>
-      <c r="K45" s="45">
+      <c r="K45" s="19">
         <v>1052</v>
       </c>
-      <c r="L45" s="45">
+      <c r="L45" s="19">
         <v>1116</v>
       </c>
-      <c r="O45" s="43"/>
+      <c r="O45" s="18"/>
     </row>
     <row r="46" spans="1:15">
       <c r="A46" s="6">
@@ -3670,37 +3667,37 @@
       <c r="B46" s="6" t="s">
         <v>67</v>
       </c>
-      <c r="C46" s="44">
+      <c r="C46" s="1">
         <v>762</v>
       </c>
-      <c r="D46" s="44">
+      <c r="D46" s="1">
         <v>786</v>
       </c>
-      <c r="E46" s="44">
+      <c r="E46" s="1">
         <v>811</v>
       </c>
-      <c r="F46" s="44">
+      <c r="F46" s="1">
         <v>837</v>
       </c>
-      <c r="G46" s="44">
+      <c r="G46" s="1">
         <v>838</v>
       </c>
-      <c r="H46" s="44">
+      <c r="H46" s="1">
         <v>866</v>
       </c>
-      <c r="I46" s="44">
+      <c r="I46" s="1">
         <v>896</v>
       </c>
-      <c r="J46" s="44">
+      <c r="J46" s="1">
         <v>936</v>
       </c>
-      <c r="K46" s="45">
+      <c r="K46" s="19">
         <v>986</v>
       </c>
-      <c r="L46" s="45">
+      <c r="L46" s="19">
         <v>1051</v>
       </c>
-      <c r="O46" s="43"/>
+      <c r="O46" s="18"/>
     </row>
     <row r="47" spans="1:15">
       <c r="A47" s="6">
@@ -3709,37 +3706,37 @@
       <c r="B47" s="6" t="s">
         <v>68</v>
       </c>
-      <c r="C47" s="44">
+      <c r="C47" s="1">
         <v>753</v>
       </c>
-      <c r="D47" s="44">
+      <c r="D47" s="1">
         <v>777</v>
       </c>
-      <c r="E47" s="44">
+      <c r="E47" s="1">
         <v>803</v>
       </c>
-      <c r="F47" s="44">
+      <c r="F47" s="1">
         <v>830</v>
       </c>
-      <c r="G47" s="44">
+      <c r="G47" s="1">
         <v>831</v>
       </c>
-      <c r="H47" s="44">
+      <c r="H47" s="1">
         <v>859</v>
       </c>
-      <c r="I47" s="44">
+      <c r="I47" s="1">
         <v>889</v>
       </c>
-      <c r="J47" s="44">
+      <c r="J47" s="1">
         <v>929</v>
       </c>
-      <c r="K47" s="45">
+      <c r="K47" s="19">
         <v>980</v>
       </c>
-      <c r="L47" s="45">
+      <c r="L47" s="19">
         <v>1045</v>
       </c>
-      <c r="O47" s="43"/>
+      <c r="O47" s="18"/>
     </row>
     <row r="48" spans="1:15">
       <c r="A48" s="6">
@@ -3748,37 +3745,37 @@
       <c r="B48" s="6" t="s">
         <v>69</v>
       </c>
-      <c r="C48" s="44">
+      <c r="C48" s="1">
         <v>715</v>
       </c>
-      <c r="D48" s="44">
+      <c r="D48" s="1">
         <v>738</v>
       </c>
-      <c r="E48" s="44">
+      <c r="E48" s="1">
         <v>762</v>
       </c>
-      <c r="F48" s="44">
+      <c r="F48" s="1">
         <v>790</v>
       </c>
-      <c r="G48" s="44">
+      <c r="G48" s="1">
         <v>792</v>
       </c>
-      <c r="H48" s="44">
+      <c r="H48" s="1">
         <v>821</v>
       </c>
-      <c r="I48" s="44">
+      <c r="I48" s="1">
         <v>854</v>
       </c>
-      <c r="J48" s="44">
+      <c r="J48" s="1">
         <v>900</v>
       </c>
-      <c r="K48" s="45">
+      <c r="K48" s="19">
         <v>957</v>
       </c>
-      <c r="L48" s="45">
+      <c r="L48" s="19">
         <v>1030</v>
       </c>
-      <c r="O48" s="43"/>
+      <c r="O48" s="18"/>
     </row>
     <row r="49" spans="1:15">
       <c r="A49" s="6">
@@ -3787,37 +3784,37 @@
       <c r="B49" s="6" t="s">
         <v>70</v>
       </c>
-      <c r="C49" s="44">
+      <c r="C49" s="1">
         <v>718</v>
       </c>
-      <c r="D49" s="44">
+      <c r="D49" s="1">
         <v>740</v>
       </c>
-      <c r="E49" s="44">
+      <c r="E49" s="1">
         <v>764</v>
       </c>
-      <c r="F49" s="44">
+      <c r="F49" s="1">
         <v>790</v>
       </c>
-      <c r="G49" s="44">
+      <c r="G49" s="1">
         <v>792</v>
       </c>
-      <c r="H49" s="44">
+      <c r="H49" s="1">
         <v>824</v>
       </c>
-      <c r="I49" s="44">
+      <c r="I49" s="1">
         <v>857</v>
       </c>
-      <c r="J49" s="44">
+      <c r="J49" s="1">
         <v>904</v>
       </c>
-      <c r="K49" s="45">
+      <c r="K49" s="19">
         <v>962</v>
       </c>
-      <c r="L49" s="45">
+      <c r="L49" s="19">
         <v>1033</v>
       </c>
-      <c r="O49" s="43"/>
+      <c r="O49" s="18"/>
     </row>
     <row r="50" spans="1:15">
       <c r="A50" s="6">
@@ -3826,37 +3823,37 @@
       <c r="B50" s="6" t="s">
         <v>71</v>
       </c>
-      <c r="C50" s="44">
+      <c r="C50" s="1">
         <v>757</v>
       </c>
-      <c r="D50" s="44">
+      <c r="D50" s="1">
         <v>781</v>
       </c>
-      <c r="E50" s="44">
+      <c r="E50" s="1">
         <v>807</v>
       </c>
-      <c r="F50" s="44">
+      <c r="F50" s="1">
         <v>833</v>
       </c>
-      <c r="G50" s="44">
+      <c r="G50" s="1">
         <v>834</v>
       </c>
-      <c r="H50" s="44">
+      <c r="H50" s="1">
         <v>862</v>
       </c>
-      <c r="I50" s="44">
+      <c r="I50" s="1">
         <v>892</v>
       </c>
-      <c r="J50" s="44">
+      <c r="J50" s="1">
         <v>932</v>
       </c>
-      <c r="K50" s="45">
+      <c r="K50" s="19">
         <v>982</v>
       </c>
-      <c r="L50" s="45">
+      <c r="L50" s="19">
         <v>1047</v>
       </c>
-      <c r="O50" s="43"/>
+      <c r="O50" s="18"/>
     </row>
     <row r="51" spans="1:15">
       <c r="A51" s="6">
@@ -3865,37 +3862,37 @@
       <c r="B51" s="6" t="s">
         <v>72</v>
       </c>
-      <c r="C51" s="44">
+      <c r="C51" s="1">
         <v>793</v>
       </c>
-      <c r="D51" s="44">
+      <c r="D51" s="1">
         <v>818</v>
       </c>
-      <c r="E51" s="44">
+      <c r="E51" s="1">
         <v>844</v>
       </c>
-      <c r="F51" s="44">
+      <c r="F51" s="1">
         <v>871</v>
       </c>
-      <c r="G51" s="44">
+      <c r="G51" s="1">
         <v>871</v>
       </c>
-      <c r="H51" s="44">
+      <c r="H51" s="1">
         <v>899</v>
       </c>
-      <c r="I51" s="44">
+      <c r="I51" s="1">
         <v>930</v>
       </c>
-      <c r="J51" s="44">
+      <c r="J51" s="1">
         <v>970</v>
       </c>
-      <c r="K51" s="45">
+      <c r="K51" s="19">
         <v>1020</v>
       </c>
-      <c r="L51" s="45">
+      <c r="L51" s="19">
         <v>1085</v>
       </c>
-      <c r="O51" s="43"/>
+      <c r="O51" s="18"/>
     </row>
     <row r="52" spans="1:15">
       <c r="A52" s="6">
@@ -3904,37 +3901,37 @@
       <c r="B52" s="6" t="s">
         <v>73</v>
       </c>
-      <c r="C52" s="44">
+      <c r="C52" s="1">
         <v>753</v>
       </c>
-      <c r="D52" s="44">
+      <c r="D52" s="1">
         <v>777</v>
       </c>
-      <c r="E52" s="44">
+      <c r="E52" s="1">
         <v>802</v>
       </c>
-      <c r="F52" s="44">
+      <c r="F52" s="1">
         <v>829</v>
       </c>
-      <c r="G52" s="44">
+      <c r="G52" s="1">
         <v>829</v>
       </c>
-      <c r="H52" s="44">
+      <c r="H52" s="1">
         <v>857</v>
       </c>
-      <c r="I52" s="44">
+      <c r="I52" s="1">
         <v>888</v>
       </c>
-      <c r="J52" s="44">
+      <c r="J52" s="1">
         <v>928</v>
       </c>
-      <c r="K52" s="45">
+      <c r="K52" s="19">
         <v>979</v>
       </c>
-      <c r="L52" s="45">
+      <c r="L52" s="19">
         <v>1043</v>
       </c>
-      <c r="O52" s="43"/>
+      <c r="O52" s="18"/>
     </row>
     <row r="53" spans="1:15">
       <c r="A53" s="6">
@@ -3943,37 +3940,37 @@
       <c r="B53" s="6" t="s">
         <v>74</v>
       </c>
-      <c r="C53" s="44">
+      <c r="C53" s="1">
         <v>716</v>
       </c>
-      <c r="D53" s="44">
+      <c r="D53" s="1">
         <v>740</v>
       </c>
-      <c r="E53" s="44">
+      <c r="E53" s="1">
         <v>766</v>
       </c>
-      <c r="F53" s="44">
+      <c r="F53" s="1">
         <v>793</v>
       </c>
-      <c r="G53" s="44">
+      <c r="G53" s="1">
         <v>796</v>
       </c>
-      <c r="H53" s="44">
+      <c r="H53" s="1">
         <v>824</v>
       </c>
-      <c r="I53" s="44">
+      <c r="I53" s="1">
         <v>855</v>
       </c>
-      <c r="J53" s="44">
+      <c r="J53" s="1">
         <v>896</v>
       </c>
-      <c r="K53" s="45">
+      <c r="K53" s="19">
         <v>980</v>
       </c>
-      <c r="L53" s="45">
+      <c r="L53" s="19">
         <v>1046</v>
       </c>
-      <c r="O53" s="43"/>
+      <c r="O53" s="18"/>
     </row>
     <row r="54" spans="1:15">
       <c r="A54" s="6">
@@ -3982,37 +3979,37 @@
       <c r="B54" s="6" t="s">
         <v>75</v>
       </c>
-      <c r="C54" s="44">
+      <c r="C54" s="1">
         <v>742</v>
       </c>
-      <c r="D54" s="44">
+      <c r="D54" s="1">
         <v>766</v>
       </c>
-      <c r="E54" s="44">
+      <c r="E54" s="1">
         <v>792</v>
       </c>
-      <c r="F54" s="44">
+      <c r="F54" s="1">
         <v>818</v>
       </c>
-      <c r="G54" s="44">
+      <c r="G54" s="1">
         <v>820</v>
       </c>
-      <c r="H54" s="44">
+      <c r="H54" s="1">
         <v>848</v>
       </c>
-      <c r="I54" s="44">
+      <c r="I54" s="1">
         <v>878</v>
       </c>
-      <c r="J54" s="44">
+      <c r="J54" s="1">
         <v>918</v>
       </c>
-      <c r="K54" s="45">
+      <c r="K54" s="19">
         <v>970</v>
       </c>
-      <c r="L54" s="45">
+      <c r="L54" s="19">
         <v>1036</v>
       </c>
-      <c r="O54" s="43"/>
+      <c r="O54" s="18"/>
     </row>
     <row r="55" spans="1:15">
       <c r="A55" s="6">
@@ -4021,37 +4018,37 @@
       <c r="B55" s="6" t="s">
         <v>76</v>
       </c>
-      <c r="C55" s="44">
+      <c r="C55" s="1">
         <v>717</v>
       </c>
-      <c r="D55" s="44">
+      <c r="D55" s="1">
         <v>739</v>
       </c>
-      <c r="E55" s="44">
+      <c r="E55" s="1">
         <v>764</v>
       </c>
-      <c r="F55" s="44">
+      <c r="F55" s="1">
         <v>790</v>
       </c>
-      <c r="G55" s="44">
+      <c r="G55" s="1">
         <v>793</v>
       </c>
-      <c r="H55" s="44">
+      <c r="H55" s="1">
         <v>821</v>
       </c>
-      <c r="I55" s="44">
+      <c r="I55" s="1">
         <v>853</v>
       </c>
-      <c r="J55" s="44">
+      <c r="J55" s="1">
         <v>897</v>
       </c>
-      <c r="K55" s="45">
+      <c r="K55" s="19">
         <v>956</v>
       </c>
-      <c r="L55" s="45">
+      <c r="L55" s="19">
         <v>1033</v>
       </c>
-      <c r="O55" s="43"/>
+      <c r="O55" s="18"/>
     </row>
     <row r="56" spans="1:15">
       <c r="A56" s="6">
@@ -4060,37 +4057,37 @@
       <c r="B56" s="6" t="s">
         <v>77</v>
       </c>
-      <c r="C56" s="44">
+      <c r="C56" s="1">
         <v>715</v>
       </c>
-      <c r="D56" s="44">
+      <c r="D56" s="1">
         <v>737</v>
       </c>
-      <c r="E56" s="44">
+      <c r="E56" s="1">
         <v>762</v>
       </c>
-      <c r="F56" s="44">
+      <c r="F56" s="1">
         <v>790</v>
       </c>
-      <c r="G56" s="44">
+      <c r="G56" s="1">
         <v>792</v>
       </c>
-      <c r="H56" s="44">
+      <c r="H56" s="1">
         <v>820</v>
       </c>
-      <c r="I56" s="44">
+      <c r="I56" s="1">
         <v>853</v>
       </c>
-      <c r="J56" s="44">
+      <c r="J56" s="1">
         <v>897</v>
       </c>
-      <c r="K56" s="45">
+      <c r="K56" s="19">
         <v>952</v>
       </c>
-      <c r="L56" s="45">
+      <c r="L56" s="19">
         <v>1023</v>
       </c>
-      <c r="O56" s="43"/>
+      <c r="O56" s="18"/>
     </row>
     <row r="57" spans="1:15">
       <c r="A57" s="6">
@@ -4099,37 +4096,37 @@
       <c r="B57" s="6" t="s">
         <v>78</v>
       </c>
-      <c r="C57" s="44">
+      <c r="C57" s="1">
         <v>765</v>
       </c>
-      <c r="D57" s="44">
+      <c r="D57" s="1">
         <v>789</v>
       </c>
-      <c r="E57" s="44">
+      <c r="E57" s="1">
         <v>814</v>
       </c>
-      <c r="F57" s="44">
+      <c r="F57" s="1">
         <v>841</v>
       </c>
-      <c r="G57" s="44">
+      <c r="G57" s="1">
         <v>842</v>
       </c>
-      <c r="H57" s="44">
+      <c r="H57" s="1">
         <v>870</v>
       </c>
-      <c r="I57" s="44">
+      <c r="I57" s="1">
         <v>900</v>
       </c>
-      <c r="J57" s="44">
+      <c r="J57" s="1">
         <v>941</v>
       </c>
-      <c r="K57" s="45">
+      <c r="K57" s="19">
         <v>992</v>
       </c>
-      <c r="L57" s="45">
+      <c r="L57" s="19">
         <v>1057</v>
       </c>
-      <c r="O57" s="43"/>
+      <c r="O57" s="18"/>
     </row>
     <row r="58" spans="1:15">
       <c r="A58" s="6">
@@ -4138,37 +4135,37 @@
       <c r="B58" s="6" t="s">
         <v>79</v>
       </c>
-      <c r="C58" s="44">
+      <c r="C58" s="1">
         <v>715</v>
       </c>
-      <c r="D58" s="44">
+      <c r="D58" s="1">
         <v>737</v>
       </c>
-      <c r="E58" s="44">
+      <c r="E58" s="1">
         <v>762</v>
       </c>
-      <c r="F58" s="44">
+      <c r="F58" s="1">
         <v>790</v>
       </c>
-      <c r="G58" s="44">
+      <c r="G58" s="1">
         <v>792</v>
       </c>
-      <c r="H58" s="44">
+      <c r="H58" s="1">
         <v>821</v>
       </c>
-      <c r="I58" s="44">
+      <c r="I58" s="1">
         <v>853</v>
       </c>
-      <c r="J58" s="44">
+      <c r="J58" s="1">
         <v>900</v>
       </c>
-      <c r="K58" s="45">
+      <c r="K58" s="19">
         <v>956</v>
       </c>
-      <c r="L58" s="45">
+      <c r="L58" s="19">
         <v>1030</v>
       </c>
-      <c r="O58" s="43"/>
+      <c r="O58" s="18"/>
     </row>
     <row r="59" spans="1:15">
       <c r="A59" s="6">
@@ -4177,37 +4174,37 @@
       <c r="B59" s="6" t="s">
         <v>80</v>
       </c>
-      <c r="C59" s="44">
+      <c r="C59" s="1">
         <v>715</v>
       </c>
-      <c r="D59" s="44">
+      <c r="D59" s="1">
         <v>737</v>
       </c>
-      <c r="E59" s="44">
+      <c r="E59" s="1">
         <v>762</v>
       </c>
-      <c r="F59" s="44">
+      <c r="F59" s="1">
         <v>790</v>
       </c>
-      <c r="G59" s="44">
+      <c r="G59" s="1">
         <v>793</v>
       </c>
-      <c r="H59" s="44">
+      <c r="H59" s="1">
         <v>821</v>
       </c>
-      <c r="I59" s="44">
+      <c r="I59" s="1">
         <v>853</v>
       </c>
-      <c r="J59" s="44">
+      <c r="J59" s="1">
         <v>898</v>
       </c>
-      <c r="K59" s="45">
+      <c r="K59" s="19">
         <v>953</v>
       </c>
-      <c r="L59" s="45">
+      <c r="L59" s="19">
         <v>1031</v>
       </c>
-      <c r="O59" s="43"/>
+      <c r="O59" s="18"/>
     </row>
     <row r="60" spans="1:15">
       <c r="A60" s="6">
@@ -4216,37 +4213,37 @@
       <c r="B60" s="6" t="s">
         <v>81</v>
       </c>
-      <c r="C60" s="44">
+      <c r="C60" s="1">
         <v>715</v>
       </c>
-      <c r="D60" s="44">
+      <c r="D60" s="1">
         <v>737</v>
       </c>
-      <c r="E60" s="44">
+      <c r="E60" s="1">
         <v>762</v>
       </c>
-      <c r="F60" s="44">
+      <c r="F60" s="1">
         <v>790</v>
       </c>
-      <c r="G60" s="44">
+      <c r="G60" s="1">
         <v>793</v>
       </c>
-      <c r="H60" s="44">
+      <c r="H60" s="1">
         <v>821</v>
       </c>
-      <c r="I60" s="44">
+      <c r="I60" s="1">
         <v>853</v>
       </c>
-      <c r="J60" s="44">
+      <c r="J60" s="1">
         <v>898</v>
       </c>
-      <c r="K60" s="45">
+      <c r="K60" s="19">
         <v>952</v>
       </c>
-      <c r="L60" s="45">
+      <c r="L60" s="19">
         <v>1034</v>
       </c>
-      <c r="O60" s="43"/>
+      <c r="O60" s="18"/>
     </row>
     <row r="61" spans="1:15">
       <c r="A61" s="6">
@@ -4255,37 +4252,37 @@
       <c r="B61" s="6" t="s">
         <v>82</v>
       </c>
-      <c r="C61" s="44">
+      <c r="C61" s="1">
         <v>715</v>
       </c>
-      <c r="D61" s="44">
+      <c r="D61" s="1">
         <v>737</v>
       </c>
-      <c r="E61" s="44">
+      <c r="E61" s="1">
         <v>762</v>
       </c>
-      <c r="F61" s="44">
+      <c r="F61" s="1">
         <v>790</v>
       </c>
-      <c r="G61" s="44">
+      <c r="G61" s="1">
         <v>792</v>
       </c>
-      <c r="H61" s="44">
+      <c r="H61" s="1">
         <v>822</v>
       </c>
-      <c r="I61" s="44">
+      <c r="I61" s="1">
         <v>854</v>
       </c>
-      <c r="J61" s="44">
+      <c r="J61" s="1">
         <v>899</v>
       </c>
-      <c r="K61" s="45">
+      <c r="K61" s="19">
         <v>954</v>
       </c>
-      <c r="L61" s="45">
+      <c r="L61" s="19">
         <v>1035</v>
       </c>
-      <c r="O61" s="43"/>
+      <c r="O61" s="18"/>
     </row>
     <row r="62" spans="1:15">
       <c r="A62" s="6">
@@ -4294,37 +4291,37 @@
       <c r="B62" s="6" t="s">
         <v>83</v>
       </c>
-      <c r="C62" s="44">
+      <c r="C62" s="1">
         <v>714</v>
       </c>
-      <c r="D62" s="44">
+      <c r="D62" s="1">
         <v>737</v>
       </c>
-      <c r="E62" s="44">
+      <c r="E62" s="1">
         <v>762</v>
       </c>
-      <c r="F62" s="44">
+      <c r="F62" s="1">
         <v>790</v>
       </c>
-      <c r="G62" s="44">
+      <c r="G62" s="1">
         <v>793</v>
       </c>
-      <c r="H62" s="44">
+      <c r="H62" s="1">
         <v>821</v>
       </c>
-      <c r="I62" s="44">
+      <c r="I62" s="1">
         <v>853</v>
       </c>
-      <c r="J62" s="44">
+      <c r="J62" s="1">
         <v>897</v>
       </c>
-      <c r="K62" s="45">
+      <c r="K62" s="19">
         <v>952</v>
       </c>
-      <c r="L62" s="45">
+      <c r="L62" s="19">
         <v>1023</v>
       </c>
-      <c r="O62" s="43"/>
+      <c r="O62" s="18"/>
     </row>
     <row r="63" spans="1:15">
       <c r="A63" s="6">
@@ -4333,37 +4330,37 @@
       <c r="B63" s="6" t="s">
         <v>84</v>
       </c>
-      <c r="C63" s="44">
+      <c r="C63" s="1">
         <v>715</v>
       </c>
-      <c r="D63" s="44">
+      <c r="D63" s="1">
         <v>737</v>
       </c>
-      <c r="E63" s="44">
+      <c r="E63" s="1">
         <v>761</v>
       </c>
-      <c r="F63" s="44">
+      <c r="F63" s="1">
         <v>790</v>
       </c>
-      <c r="G63" s="44">
+      <c r="G63" s="1">
         <v>793</v>
       </c>
-      <c r="H63" s="44">
+      <c r="H63" s="1">
         <v>821</v>
       </c>
-      <c r="I63" s="44">
+      <c r="I63" s="1">
         <v>853</v>
       </c>
-      <c r="J63" s="44">
+      <c r="J63" s="1">
         <v>897</v>
       </c>
-      <c r="K63" s="45">
+      <c r="K63" s="19">
         <v>953</v>
       </c>
-      <c r="L63" s="45">
+      <c r="L63" s="19">
         <v>1026</v>
       </c>
-      <c r="O63" s="43"/>
+      <c r="O63" s="18"/>
     </row>
     <row r="64" spans="1:15">
       <c r="A64" s="6">
@@ -4372,37 +4369,37 @@
       <c r="B64" s="6" t="s">
         <v>85</v>
       </c>
-      <c r="C64" s="44">
+      <c r="C64" s="1">
         <v>714</v>
       </c>
-      <c r="D64" s="44">
+      <c r="D64" s="1">
         <v>737</v>
       </c>
-      <c r="E64" s="44">
+      <c r="E64" s="1">
         <v>762</v>
       </c>
-      <c r="F64" s="44">
+      <c r="F64" s="1">
         <v>790</v>
       </c>
-      <c r="G64" s="44">
+      <c r="G64" s="1">
         <v>792</v>
       </c>
-      <c r="H64" s="44">
+      <c r="H64" s="1">
         <v>820</v>
       </c>
-      <c r="I64" s="44">
+      <c r="I64" s="1">
         <v>853</v>
       </c>
-      <c r="J64" s="44">
+      <c r="J64" s="1">
         <v>896</v>
       </c>
-      <c r="K64" s="45">
+      <c r="K64" s="19">
         <v>952</v>
       </c>
-      <c r="L64" s="45">
+      <c r="L64" s="19">
         <v>1023</v>
       </c>
-      <c r="O64" s="43"/>
+      <c r="O64" s="18"/>
     </row>
   </sheetData>
   <mergeCells count="3">
@@ -4425,43 +4422,43 @@
   <sheetData>
     <row r="1" spans="1:14">
       <c r="A1" s="16" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
     </row>
     <row r="2" spans="1:14">
       <c r="A2" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
     </row>
     <row r="4" spans="1:14">
-      <c r="C4" s="25" t="s">
+      <c r="C4" s="28" t="s">
         <v>88</v>
       </c>
-      <c r="D4" s="26"/>
-      <c r="E4" s="26"/>
-      <c r="F4" s="26"/>
-      <c r="G4" s="26"/>
-      <c r="H4" s="26"/>
-      <c r="I4" s="26"/>
-      <c r="J4" s="26"/>
-      <c r="K4" s="26"/>
-      <c r="L4" s="26"/>
-      <c r="M4" s="26"/>
-      <c r="N4" s="27"/>
+      <c r="D4" s="29"/>
+      <c r="E4" s="29"/>
+      <c r="F4" s="29"/>
+      <c r="G4" s="29"/>
+      <c r="H4" s="29"/>
+      <c r="I4" s="29"/>
+      <c r="J4" s="29"/>
+      <c r="K4" s="29"/>
+      <c r="L4" s="29"/>
+      <c r="M4" s="29"/>
+      <c r="N4" s="30"/>
     </row>
     <row r="5" spans="1:14" ht="15" thickBot="1">
-      <c r="C5" s="28"/>
-      <c r="D5" s="29"/>
-      <c r="E5" s="29"/>
-      <c r="F5" s="32"/>
-      <c r="G5" s="32"/>
-      <c r="H5" s="32"/>
-      <c r="I5" s="32"/>
-      <c r="J5" s="32"/>
-      <c r="K5" s="32"/>
-      <c r="L5" s="32"/>
-      <c r="M5" s="32"/>
-      <c r="N5" s="33"/>
+      <c r="C5" s="31"/>
+      <c r="D5" s="32"/>
+      <c r="E5" s="32"/>
+      <c r="F5" s="35"/>
+      <c r="G5" s="35"/>
+      <c r="H5" s="35"/>
+      <c r="I5" s="35"/>
+      <c r="J5" s="35"/>
+      <c r="K5" s="35"/>
+      <c r="L5" s="35"/>
+      <c r="M5" s="35"/>
+      <c r="N5" s="36"/>
     </row>
     <row r="6" spans="1:14" ht="15" thickBot="1">
       <c r="C6" s="11" t="s">
@@ -4475,48 +4472,48 @@
       </c>
     </row>
     <row r="8" spans="1:14" ht="14.55" customHeight="1">
-      <c r="C8" s="25" t="s">
-        <v>149</v>
-      </c>
-      <c r="D8" s="26"/>
-      <c r="E8" s="26"/>
-      <c r="F8" s="26"/>
-      <c r="G8" s="26"/>
-      <c r="H8" s="26"/>
-      <c r="I8" s="26"/>
-      <c r="J8" s="26"/>
-      <c r="K8" s="26"/>
-      <c r="L8" s="26"/>
-      <c r="M8" s="26"/>
-      <c r="N8" s="27"/>
+      <c r="C8" s="28" t="s">
+        <v>147</v>
+      </c>
+      <c r="D8" s="29"/>
+      <c r="E8" s="29"/>
+      <c r="F8" s="29"/>
+      <c r="G8" s="29"/>
+      <c r="H8" s="29"/>
+      <c r="I8" s="29"/>
+      <c r="J8" s="29"/>
+      <c r="K8" s="29"/>
+      <c r="L8" s="29"/>
+      <c r="M8" s="29"/>
+      <c r="N8" s="30"/>
     </row>
     <row r="9" spans="1:14">
-      <c r="C9" s="28"/>
-      <c r="D9" s="29"/>
-      <c r="E9" s="29"/>
-      <c r="F9" s="29"/>
-      <c r="G9" s="29"/>
-      <c r="H9" s="29"/>
-      <c r="I9" s="29"/>
-      <c r="J9" s="29"/>
-      <c r="K9" s="29"/>
-      <c r="L9" s="29"/>
-      <c r="M9" s="29"/>
-      <c r="N9" s="30"/>
+      <c r="C9" s="31"/>
+      <c r="D9" s="32"/>
+      <c r="E9" s="32"/>
+      <c r="F9" s="32"/>
+      <c r="G9" s="32"/>
+      <c r="H9" s="32"/>
+      <c r="I9" s="32"/>
+      <c r="J9" s="32"/>
+      <c r="K9" s="32"/>
+      <c r="L9" s="32"/>
+      <c r="M9" s="32"/>
+      <c r="N9" s="33"/>
     </row>
     <row r="10" spans="1:14" ht="15" thickBot="1">
-      <c r="C10" s="28"/>
-      <c r="D10" s="29"/>
-      <c r="E10" s="29"/>
-      <c r="F10" s="32"/>
-      <c r="G10" s="32"/>
-      <c r="H10" s="32"/>
-      <c r="I10" s="32"/>
-      <c r="J10" s="32"/>
-      <c r="K10" s="32"/>
-      <c r="L10" s="32"/>
-      <c r="M10" s="32"/>
-      <c r="N10" s="33"/>
+      <c r="C10" s="31"/>
+      <c r="D10" s="32"/>
+      <c r="E10" s="32"/>
+      <c r="F10" s="35"/>
+      <c r="G10" s="35"/>
+      <c r="H10" s="35"/>
+      <c r="I10" s="35"/>
+      <c r="J10" s="35"/>
+      <c r="K10" s="35"/>
+      <c r="L10" s="35"/>
+      <c r="M10" s="35"/>
+      <c r="N10" s="36"/>
     </row>
     <row r="11" spans="1:14" ht="15" thickBot="1">
       <c r="C11" s="11" t="s">
@@ -4537,40 +4534,40 @@
         <v>86</v>
       </c>
       <c r="C13" s="10" t="s">
+        <v>131</v>
+      </c>
+      <c r="D13" s="10" t="s">
+        <v>132</v>
+      </c>
+      <c r="E13" s="10" t="s">
         <v>133</v>
       </c>
-      <c r="D13" s="10" t="s">
+      <c r="F13" s="10" t="s">
         <v>134</v>
       </c>
-      <c r="E13" s="10" t="s">
+      <c r="G13" s="10" t="s">
         <v>135</v>
       </c>
-      <c r="F13" s="10" t="s">
+      <c r="H13" s="10" t="s">
         <v>136</v>
       </c>
-      <c r="G13" s="10" t="s">
+      <c r="I13" s="10" t="s">
         <v>137</v>
       </c>
-      <c r="H13" s="10" t="s">
+      <c r="J13" s="10" t="s">
         <v>138</v>
       </c>
-      <c r="I13" s="10" t="s">
+      <c r="K13" s="10" t="s">
         <v>139</v>
       </c>
-      <c r="J13" s="10" t="s">
+      <c r="L13" s="10" t="s">
         <v>140</v>
       </c>
-      <c r="K13" s="10" t="s">
+      <c r="M13" s="10" t="s">
         <v>141</v>
       </c>
-      <c r="L13" s="10" t="s">
+      <c r="N13" s="10" t="s">
         <v>142</v>
-      </c>
-      <c r="M13" s="10" t="s">
-        <v>143</v>
-      </c>
-      <c r="N13" s="10" t="s">
-        <v>144</v>
       </c>
     </row>
     <row r="14" spans="1:14">
@@ -6701,16 +6698,16 @@
         <v>109</v>
       </c>
       <c r="J5" s="7" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="K5" s="7" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="L5" s="7" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="M5" s="7" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
     </row>
     <row r="6" spans="1:13">
@@ -6970,28 +6967,28 @@
       </c>
     </row>
     <row r="14" spans="1:13">
-      <c r="A14" s="19" t="s">
-        <v>124</v>
-      </c>
-      <c r="B14" s="20"/>
-      <c r="C14" s="20"/>
-      <c r="D14" s="20"/>
-      <c r="E14" s="20"/>
-      <c r="F14" s="20"/>
-      <c r="G14" s="20"/>
-      <c r="H14" s="20"/>
-      <c r="I14" s="21"/>
+      <c r="A14" s="22" t="s">
+        <v>158</v>
+      </c>
+      <c r="B14" s="23"/>
+      <c r="C14" s="23"/>
+      <c r="D14" s="23"/>
+      <c r="E14" s="23"/>
+      <c r="F14" s="23"/>
+      <c r="G14" s="23"/>
+      <c r="H14" s="23"/>
+      <c r="I14" s="24"/>
     </row>
     <row r="15" spans="1:13">
-      <c r="A15" s="22"/>
-      <c r="B15" s="23"/>
-      <c r="C15" s="23"/>
-      <c r="D15" s="23"/>
-      <c r="E15" s="23"/>
-      <c r="F15" s="23"/>
-      <c r="G15" s="23"/>
-      <c r="H15" s="23"/>
-      <c r="I15" s="24"/>
+      <c r="A15" s="25"/>
+      <c r="B15" s="26"/>
+      <c r="C15" s="26"/>
+      <c r="D15" s="26"/>
+      <c r="E15" s="26"/>
+      <c r="F15" s="26"/>
+      <c r="G15" s="26"/>
+      <c r="H15" s="26"/>
+      <c r="I15" s="27"/>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -7008,12 +7005,12 @@
   <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
     <col min="1" max="1" width="18.6640625" customWidth="1"/>
-    <col min="2" max="13" width="6.6640625" customWidth="1"/>
+    <col min="2" max="13" width="7.21875" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:13">
       <c r="A1" s="16" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
     </row>
     <row r="2" spans="1:13">
@@ -7231,7 +7228,7 @@
     </row>
     <row r="10" spans="1:13">
       <c r="A10" s="6" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="B10" s="1">
         <v>0.7</v>
@@ -7271,36 +7268,36 @@
       </c>
     </row>
     <row r="13" spans="1:13">
-      <c r="A13" s="19" t="s">
-        <v>125</v>
-      </c>
-      <c r="B13" s="20"/>
-      <c r="C13" s="20"/>
-      <c r="D13" s="20"/>
-      <c r="E13" s="20"/>
-      <c r="F13" s="20"/>
-      <c r="G13" s="20"/>
-      <c r="H13" s="20"/>
-      <c r="I13" s="20"/>
-      <c r="J13" s="20"/>
-      <c r="K13" s="20"/>
-      <c r="L13" s="20"/>
-      <c r="M13" s="21"/>
+      <c r="A13" s="22" t="s">
+        <v>157</v>
+      </c>
+      <c r="B13" s="23"/>
+      <c r="C13" s="23"/>
+      <c r="D13" s="23"/>
+      <c r="E13" s="23"/>
+      <c r="F13" s="23"/>
+      <c r="G13" s="23"/>
+      <c r="H13" s="23"/>
+      <c r="I13" s="23"/>
+      <c r="J13" s="23"/>
+      <c r="K13" s="23"/>
+      <c r="L13" s="23"/>
+      <c r="M13" s="24"/>
     </row>
     <row r="14" spans="1:13">
-      <c r="A14" s="22"/>
-      <c r="B14" s="23"/>
-      <c r="C14" s="23"/>
-      <c r="D14" s="23"/>
-      <c r="E14" s="23"/>
-      <c r="F14" s="23"/>
-      <c r="G14" s="23"/>
-      <c r="H14" s="23"/>
-      <c r="I14" s="23"/>
-      <c r="J14" s="23"/>
-      <c r="K14" s="23"/>
-      <c r="L14" s="23"/>
-      <c r="M14" s="24"/>
+      <c r="A14" s="25"/>
+      <c r="B14" s="26"/>
+      <c r="C14" s="26"/>
+      <c r="D14" s="26"/>
+      <c r="E14" s="26"/>
+      <c r="F14" s="26"/>
+      <c r="G14" s="26"/>
+      <c r="H14" s="26"/>
+      <c r="I14" s="26"/>
+      <c r="J14" s="26"/>
+      <c r="K14" s="26"/>
+      <c r="L14" s="26"/>
+      <c r="M14" s="27"/>
     </row>
   </sheetData>
   <mergeCells count="1">
